--- a/Tools/Luban/DataTables/Datas/CozyYard/language.xlsx
+++ b/Tools/Luban/DataTables/Datas/CozyYard/language.xlsx
@@ -30,7 +30,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,10 +441,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -460,30 +469,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>键名</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>season_spring</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>春</t>
         </is>
       </c>
     </row>
@@ -491,12 +504,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>season_summer</t>
+          <t>season_spring</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>夏</t>
+          <t>春</t>
         </is>
       </c>
     </row>
@@ -504,12 +517,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>season_autumn</t>
+          <t>season_summer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>秋</t>
+          <t>夏</t>
         </is>
       </c>
     </row>
@@ -517,12 +530,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>season_winter</t>
+          <t>season_autumn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>冬</t>
+          <t>秋</t>
         </is>
       </c>
     </row>
@@ -530,12 +543,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phase_dawn</t>
+          <t>season_winter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>清晨</t>
+          <t>冬</t>
         </is>
       </c>
     </row>
@@ -543,12 +556,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phase_morning</t>
+          <t>phase_dawn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上午</t>
+          <t>清晨</t>
         </is>
       </c>
     </row>
@@ -556,12 +569,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phase_noon</t>
+          <t>phase_morning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>正午</t>
+          <t>上午</t>
         </is>
       </c>
     </row>
@@ -569,12 +582,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phase_afternoon</t>
+          <t>phase_noon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>正午</t>
         </is>
       </c>
     </row>
@@ -582,12 +595,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phase_evening</t>
+          <t>phase_afternoon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>傍晚</t>
+          <t>下午</t>
         </is>
       </c>
     </row>
@@ -595,10 +608,23 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
+          <t>phase_evening</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>傍晚</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>phase_night</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
